--- a/data/trans_camb/P1421-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1421-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,1</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,03</t>
+          <t>-2,5; 0,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,71</t>
+          <t>-2,18; 0,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,59</t>
+          <t>-0,64; 2,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,9</t>
+          <t>-1,6; 2,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,7</t>
+          <t>-0,41; 3,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,96</t>
+          <t>3,91; 8,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,88</t>
+          <t>-1,51; 0,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,1</t>
+          <t>-0,94; 1,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,68</t>
+          <t>2,54; 5,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>118,26%</t>
+          <t>106,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107,42%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,1; 7,22</t>
+          <t>-70,58; 5,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,06; 35,18</t>
+          <t>-59,37; 37,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 165,11</t>
+          <t>-20,35; 141,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 38,84</t>
+          <t>-24,31; 43,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 73,1</t>
+          <t>-9,1; 78,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,92; 201,22</t>
+          <t>57,99; 170,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 23,65</t>
+          <t>-29,89; 26,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 56,55</t>
+          <t>-18,26; 48,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,35; 167,87</t>
+          <t>49,78; 149,4</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>4,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,18</t>
+          <t>-1,57; 0,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,03</t>
+          <t>-1,61; 0,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,9</t>
+          <t>1,82; 4,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,65</t>
+          <t>-2,47; 0,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,68</t>
+          <t>-2,46; 0,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,37</t>
+          <t>4,05; 7,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,09</t>
+          <t>-1,72; -0,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,07</t>
+          <t>-1,69; 0,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,86</t>
+          <t>3,37; 5,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142,15%</t>
+          <t>160,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>101,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>118,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 14,89</t>
+          <t>-65,25; 8,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,13; 4,15</t>
+          <t>-67,04; 12,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,4; 258,44</t>
+          <t>72,42; 324,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 13,08</t>
+          <t>-37,14; 15,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 13,41</t>
+          <t>-37,8; 9,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,53; 127,7</t>
+          <t>60,88; 157,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 2,59</t>
+          <t>-40,33; -0,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 3,12</t>
+          <t>-39,91; 2,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,35; 144,54</t>
+          <t>80,32; 171,49</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>2,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -1,36</t>
+          <t>-4,46; -1,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,41</t>
+          <t>-3,51; 0,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,92</t>
+          <t>-1,43; 3,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,26</t>
+          <t>-3,92; 2,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,96</t>
+          <t>-4,17; 1,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,54</t>
+          <t>0,87; 7,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; -0,14</t>
+          <t>-3,44; 0,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,62</t>
+          <t>-2,82; 0,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,46</t>
+          <t>0,75; 4,53</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -42,71</t>
+          <t>-100,0; -43,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,75; 27,56</t>
+          <t>-79,15; 17,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 128,36</t>
+          <t>-34,35; 143,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 52,46</t>
+          <t>-50,31; 58,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 44,76</t>
+          <t>-54,01; 37,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 166,98</t>
+          <t>6,39; 150,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,81; 0,68</t>
+          <t>-60,76; 2,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,44; 17,29</t>
+          <t>-50,61; 15,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,02; 125,88</t>
+          <t>13,22; 125,73</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; -0,51</t>
+          <t>-1,78; -0,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; -0,31</t>
+          <t>-1,62; -0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,19</t>
+          <t>1,21; 3,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,77</t>
+          <t>-1,42; 0,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,89</t>
+          <t>-1,41; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,24</t>
+          <t>4,3; 6,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,12</t>
+          <t>-1,48; -0,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,13</t>
+          <t>-1,22; 0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,44</t>
+          <t>3,14; 4,75</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,17; -23,92</t>
+          <t>-65,67; -27,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,67; -14,69</t>
+          <t>-58,8; -14,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,57; 153,76</t>
+          <t>40,57; 149,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 14,95</t>
+          <t>-22,87; 11,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 17,61</t>
+          <t>-22,27; 16,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,39; 120,75</t>
+          <t>67,21; 128,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,27; -3,01</t>
+          <t>-33,42; -5,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 3,62</t>
+          <t>-27,03; 2,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52,61; 118,71</t>
+          <t>71,54; 128,22</t>
         </is>
       </c>
     </row>
